--- a/reports/2026-03-14.xlsx
+++ b/reports/2026-03-14.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trade Candidates'!$A$1:$AG$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enter Candidates'!$A$1:$AG$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enter Candidates'!$A$1:$AG$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wait Candidates'!$A$1:$AG$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-14 05:16 UTC</t>
+          <t>2026-03-14 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -642,7 +642,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-14_1773465317951</t>
+          <t>2026-03-14_1773470654209</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TRUMPUSDT</t>
+          <t>GRTUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OFFICIAL TRUMP</t>
+          <t>The Graph</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ENTER</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -930,80 +930,84 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>70</v>
+        <v>63.968</v>
       </c>
       <c r="I2" t="n">
-        <v>70</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="J2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.273047884957256</v>
+        <v>0.02640959622869432</v>
       </c>
       <c r="P2" t="n">
-        <v>4.118</v>
+        <v>0.02638</v>
       </c>
       <c r="Q2" t="n">
-        <v>25.81545228611217</v>
+        <v>-0.1120661915389953</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>at_trigger</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>3.035</v>
+        <v>0.02261</v>
       </c>
       <c r="T2" t="n">
-        <v>7.27297287801107</v>
+        <v>14.38718031048888</v>
       </c>
       <c r="U2" t="n">
-        <v>3.511095769914513</v>
+        <v>0.03020919245738865</v>
       </c>
       <c r="V2" t="n">
-        <v>3.749143654871769</v>
+        <v>0.03400878868608297</v>
       </c>
       <c r="W2" t="n">
-        <v>3.987191539829025</v>
+        <v>0.0378083849147773</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.02429248147699099</v>
+        <v>0.03791469194312642</v>
       </c>
       <c r="AA2" t="n">
-        <v>206131.8757</v>
+        <v>22533.0120156</v>
       </c>
       <c r="AB2" t="n">
-        <v>170725.24125</v>
+        <v>12251.9781237</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.187364</v>
+        <v>12.498956</v>
       </c>
       <c r="AD2" t="n">
-        <v>9.366531999999999</v>
+        <v>254.069237</v>
       </c>
       <c r="AE2" t="n">
-        <v>963082486.9768051</v>
+        <v>237286526.8349056</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -1018,12 +1022,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GRTUSDT</t>
+          <t>TURBOUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Graph</t>
+          <t>Turbo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1033,7 +1037,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1047,10 +1051,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>79.95999999999999</v>
+        <v>62.392</v>
       </c>
       <c r="I3" t="n">
-        <v>79.95999999999999</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -1074,57 +1078,57 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02640959622869432</v>
+        <v>0.001010902989841661</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02667</v>
+        <v>0.001141</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9860195099186786</v>
+        <v>12.86938622851592</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.02261</v>
+        <v>0.000876</v>
       </c>
       <c r="T3" t="n">
-        <v>14.38718031048888</v>
+        <v>13.34480075707278</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03020919245738865</v>
+        <v>0.001145805979683323</v>
       </c>
       <c r="V3" t="n">
-        <v>0.03400878868608297</v>
+        <v>0.001280708969524984</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0378083849147773</v>
+        <v>0.001415611959366646</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.999999999999999</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.07499062617172549</v>
+        <v>0.192796424502668</v>
       </c>
       <c r="AA3" t="n">
-        <v>23659.2173889</v>
+        <v>9881.433054928</v>
       </c>
       <c r="AB3" t="n">
-        <v>9723.495884900001</v>
+        <v>8495.584516289</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.878727</v>
+        <v>37.834685</v>
       </c>
       <c r="AD3" t="n">
-        <v>368.625046</v>
+        <v>369.950816</v>
       </c>
       <c r="AE3" t="n">
-        <v>234117444.5360853</v>
+        <v>79003732.82059467</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -1139,12 +1143,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TURBOUSDT</t>
+          <t>ALGOUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Turbo</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1154,7 +1158,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1168,10 +1172,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>77.98999999999999</v>
+        <v>62.184</v>
       </c>
       <c r="I4" t="n">
-        <v>77.98999999999999</v>
+        <v>77.73</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1183,25 +1187,25 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001010902989841661</v>
+        <v>0.0881281822103617</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0011675</v>
+        <v>0.09217</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.4908049270748</v>
+        <v>4.58629429118429</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1209,19 +1213,19 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.000876</v>
+        <v>0.0806</v>
       </c>
       <c r="T4" t="n">
-        <v>13.34480075707278</v>
+        <v>8.542309646637152</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001145805979683323</v>
+        <v>0.09565636442072339</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001280708969524984</v>
+        <v>0.1031845466310851</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001415611959366646</v>
+        <v>0.1107127288414468</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -1230,22 +1234,22 @@
         <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1109830537414168</v>
+        <v>0.1086130118388063</v>
       </c>
       <c r="AA4" t="n">
-        <v>13996.687216901</v>
+        <v>58469.0676636</v>
       </c>
       <c r="AB4" t="n">
-        <v>9804.828149494</v>
+        <v>54732.5031165</v>
       </c>
       <c r="AC4" t="n">
-        <v>40.428812</v>
+        <v>26.451381</v>
       </c>
       <c r="AD4" t="n">
-        <v>341.071642</v>
+        <v>30.931245</v>
       </c>
       <c r="AE4" t="n">
-        <v>80281438.96733324</v>
+        <v>821498659.5548553</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1260,12 +1264,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALGOUSDT</t>
+          <t>BANANAS31USDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Banana For Scale</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1275,33 +1279,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>77.73</v>
+        <v>61.2</v>
       </c>
       <c r="I5" t="n">
-        <v>77.73</v>
+        <v>68</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>none</t>
@@ -1316,13 +1316,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0881281822103617</v>
+        <v>0.008539124282940763</v>
       </c>
       <c r="P5" t="n">
-        <v>0.09425</v>
+        <v>0.01074</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.946492751916233</v>
+        <v>25.774021364885</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1330,19 +1330,19 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.0806</v>
+        <v>0.007486231252880395</v>
       </c>
       <c r="T5" t="n">
-        <v>8.542309646637152</v>
+        <v>12.33022257520962</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09565636442072339</v>
+        <v>0.009592017313001132</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1031845466310851</v>
+        <v>0.0106449103430615</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1107127288414468</v>
+        <v>0.01169780337312187</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -1351,22 +1351,22 @@
         <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2016449986733836</v>
+        <v>0.03074443455860293</v>
       </c>
       <c r="AA5" t="n">
-        <v>69045.23505849999</v>
+        <v>9597.195318724</v>
       </c>
       <c r="AB5" t="n">
-        <v>72640.4795687</v>
+        <v>17536.443041871</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.985773</v>
+        <v>21.126211</v>
       </c>
       <c r="AD5" t="n">
-        <v>21.205293</v>
+        <v>82.92800800000001</v>
       </c>
       <c r="AE5" t="n">
-        <v>838849995.5801125</v>
+        <v>107477184.4761735</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MELANIAUSDT</t>
+          <t>RIVERUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Official Melania Meme</t>
+          <t>River</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1396,24 +1396,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_chased</t>
+          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>75.43000000000001</v>
+        <v>61.2</v>
       </c>
       <c r="I6" t="n">
-        <v>75.43000000000001</v>
+        <v>68</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -1433,13 +1433,13 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1112803252979652</v>
+        <v>18.16763992150123</v>
       </c>
       <c r="P6" t="n">
-        <v>0.12622</v>
+        <v>21.814</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.42526152941432</v>
+        <v>20.07063159691609</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1447,19 +1447,19 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.10264</v>
+        <v>16.49196841873954</v>
       </c>
       <c r="T6" t="n">
-        <v>7.764468044849582</v>
+        <v>9.223385701180424</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1199206505959303</v>
+        <v>19.84331142426293</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1285609758938955</v>
+        <v>21.51898292702462</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1372013011918607</v>
+        <v>23.19465442978631</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -1468,33 +1468,29 @@
         <v>2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2771289441387143</v>
+        <v>0.1452886923098024</v>
       </c>
       <c r="AA6" t="n">
-        <v>2941.1854253</v>
+        <v>12996.092697</v>
       </c>
       <c r="AB6" t="n">
-        <v>3019.6961802</v>
+        <v>9155.83409</v>
       </c>
       <c r="AC6" t="n">
-        <v>82.148719</v>
+        <v>47.281283</v>
       </c>
       <c r="AD6" t="n">
-        <v>3097.201671</v>
+        <v>107.994066</v>
       </c>
       <c r="AE6" t="n">
-        <v>126640131.3049714</v>
+        <v>425424556.8357913</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>low_liquidity</t>
-        </is>
-      </c>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1502,12 +1498,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BANANAS31USDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Banana For Scale</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1517,7 +1513,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+          <t>btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1531,7 +1527,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>68</v>
+        <v>61.2</v>
       </c>
       <c r="I7" t="n">
         <v>68</v>
@@ -1542,25 +1538,25 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008539124282940763</v>
+        <v>219.1247632833021</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0109933</v>
+        <v>237.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.7403676974479</v>
+        <v>8.39943256112139</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1568,19 +1564,19 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0.007486231252880395</v>
+        <v>204.2569217840868</v>
       </c>
       <c r="T7" t="n">
-        <v>12.33022257520962</v>
+        <v>6.78510327926425</v>
       </c>
       <c r="U7" t="n">
-        <v>0.009592017313001132</v>
+        <v>233.9926047825175</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0106449103430615</v>
+        <v>248.8604462817329</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01169780337312187</v>
+        <v>263.7282877809482</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
@@ -1589,22 +1585,22 @@
         <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02823816615884125</v>
+        <v>0.05898462186643622</v>
       </c>
       <c r="AA7" t="n">
-        <v>8759.795877918001</v>
+        <v>226657.46683</v>
       </c>
       <c r="AB7" t="n">
-        <v>10741.506298575</v>
+        <v>203045.18005</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.40979</v>
+        <v>4.694521</v>
       </c>
       <c r="AD7" t="n">
-        <v>74.307877</v>
+        <v>8.198316</v>
       </c>
       <c r="AE7" t="n">
-        <v>109297486.2205953</v>
+        <v>2551194347.267691</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1619,12 +1615,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RIVERUSDT</t>
+          <t>MELANIAUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Official Melania Meme</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1634,24 +1630,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>68</v>
+        <v>60.344</v>
       </c>
       <c r="I8" t="n">
-        <v>68</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -1671,13 +1667,13 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>18.16763992150123</v>
+        <v>0.1112803252979652</v>
       </c>
       <c r="P8" t="n">
-        <v>21.58</v>
+        <v>0.12347</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.78262720553079</v>
+        <v>10.95402504386616</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1685,19 +1681,19 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>16.49196841873954</v>
+        <v>0.10264</v>
       </c>
       <c r="T8" t="n">
-        <v>9.223385701180424</v>
+        <v>7.764468044849582</v>
       </c>
       <c r="U8" t="n">
-        <v>19.84331142426293</v>
+        <v>0.1199206505959303</v>
       </c>
       <c r="V8" t="n">
-        <v>21.51898292702462</v>
+        <v>0.1285609758938955</v>
       </c>
       <c r="W8" t="n">
-        <v>23.19465442978631</v>
+        <v>0.1372013011918607</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1706,29 +1702,33 @@
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0356526872634239</v>
+        <v>0.3883180972413302</v>
       </c>
       <c r="AA8" t="n">
-        <v>15653.537735</v>
+        <v>2868.5310179</v>
       </c>
       <c r="AB8" t="n">
-        <v>16345.548524</v>
+        <v>4581.8561025</v>
       </c>
       <c r="AC8" t="n">
-        <v>26.460085</v>
+        <v>65.49919800000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>82.540488</v>
+        <v>2669.233357</v>
       </c>
       <c r="AE8" t="n">
-        <v>423313573.005538</v>
+        <v>123955104.8551496</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>low_liquidity</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1736,39 +1736,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TAOUSDT</t>
+          <t>DEEPUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>DeepBook Protocol</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>NO_TRADE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>68</v>
+        <v>73.752</v>
       </c>
       <c r="I9" t="n">
-        <v>68</v>
+        <v>92.19</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1776,25 +1776,25 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>219.1247632833021</v>
+        <v>0.02956494343623838</v>
       </c>
       <c r="P9" t="n">
-        <v>245.26</v>
+        <v>0.033455</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.92710322881587</v>
+        <v>13.15766618039085</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1802,43 +1802,43 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>204.2569217840868</v>
+        <v>0.021229</v>
       </c>
       <c r="T9" t="n">
-        <v>6.78510327926425</v>
+        <v>28.19536406087229</v>
       </c>
       <c r="U9" t="n">
-        <v>233.9926047825175</v>
+        <v>0.03790088687247675</v>
       </c>
       <c r="V9" t="n">
-        <v>248.8604462817329</v>
+        <v>0.04623683030871513</v>
       </c>
       <c r="W9" t="n">
-        <v>263.7282877809482</v>
+        <v>0.05457277374495351</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="Y9" t="n">
         <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05298445110146337</v>
+        <v>0.06278308444324912</v>
       </c>
       <c r="AA9" t="n">
-        <v>228919.5366</v>
+        <v>23243.96057886</v>
       </c>
       <c r="AB9" t="n">
-        <v>188786.67372</v>
+        <v>22980.18209754</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.717844</v>
+        <v>33.232862</v>
       </c>
       <c r="AD9" t="n">
-        <v>9.054069999999999</v>
+        <v>56.92672</v>
       </c>
       <c r="AE9" t="n">
-        <v>2626472896.404871</v>
+        <v>164765109.4499469</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEEPUSDT</t>
+          <t>FETUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DeepBook Protocol</t>
+          <t>Artificial Superintelligence Alliance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>92.19</v>
+        <v>73.688</v>
       </c>
       <c r="I10" t="n">
-        <v>92.19</v>
+        <v>92.11</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -1893,25 +1893,25 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N10" t="b">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02956494343623838</v>
+        <v>0.1595329806088012</v>
       </c>
       <c r="P10" t="n">
-        <v>0.03459</v>
+        <v>0.1789</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.99667234134568</v>
+        <v>12.13982169535821</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1919,43 +1919,43 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0.021229</v>
+        <v>0.1339</v>
       </c>
       <c r="T10" t="n">
-        <v>28.19536406087229</v>
+        <v>16.06751187809692</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03790088687247675</v>
+        <v>0.1851659612176023</v>
       </c>
       <c r="V10" t="n">
-        <v>0.04623683030871513</v>
+        <v>0.2107989418264035</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05457277374495351</v>
+        <v>0.2364319224352047</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9999999999999996</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.05493631724276989</v>
+        <v>0.0559127760693412</v>
       </c>
       <c r="AA10" t="n">
-        <v>12132.02588805</v>
+        <v>96223.940884</v>
       </c>
       <c r="AB10" t="n">
-        <v>12370.47436989</v>
+        <v>69073.163436</v>
       </c>
       <c r="AC10" t="n">
-        <v>38.120227</v>
+        <v>4.144919</v>
       </c>
       <c r="AD10" t="n">
-        <v>90.402452</v>
+        <v>11.800884</v>
       </c>
       <c r="AE10" t="n">
-        <v>169442378.6825433</v>
+        <v>404691116.8727577</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FETUSDT</t>
+          <t>CFXUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Artificial Superintelligence Alliance</t>
+          <t>Conflux</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>92.11</v>
+        <v>67.736</v>
       </c>
       <c r="I11" t="n">
-        <v>92.11</v>
+        <v>84.67</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -2010,25 +2010,25 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N11" t="b">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1595329806088012</v>
+        <v>0.05096304562042638</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1815</v>
+        <v>0.05483</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.76957874626894</v>
+        <v>7.587761548583183</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2036,19 +2036,19 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>0.1339</v>
+        <v>0.04031</v>
       </c>
       <c r="T11" t="n">
-        <v>16.06751187809692</v>
+        <v>20.90347131089936</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1851659612176023</v>
+        <v>0.06161609124085275</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2107989418264035</v>
+        <v>0.07226913686127913</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2364319224352047</v>
+        <v>0.08292218248170551</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
@@ -2057,22 +2057,22 @@
         <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.05486968449930809</v>
+        <v>0.01823985408116028</v>
       </c>
       <c r="AA11" t="n">
-        <v>102353.454086</v>
+        <v>30093.2504305</v>
       </c>
       <c r="AB11" t="n">
-        <v>69411.876397</v>
+        <v>19921.0638961</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.782798</v>
+        <v>9.505438</v>
       </c>
       <c r="AD11" t="n">
-        <v>13.184437</v>
+        <v>43.343586</v>
       </c>
       <c r="AE11" t="n">
-        <v>409784919.6575258</v>
+        <v>284758656.214079</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CFXUSDT</t>
+          <t>BERAUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Conflux</t>
+          <t>Berachain</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>84.67</v>
+        <v>66.944</v>
       </c>
       <c r="I12" t="n">
-        <v>84.67</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -2139,13 +2139,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05096304562042638</v>
+        <v>0.5830684568323188</v>
       </c>
       <c r="P12" t="n">
-        <v>0.05591</v>
+        <v>0.6249</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.706944157966202</v>
+        <v>7.174379385045571</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2153,19 +2153,19 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0.04031</v>
+        <v>0.3345</v>
       </c>
       <c r="T12" t="n">
-        <v>20.90347131089936</v>
+        <v>42.63109312802409</v>
       </c>
       <c r="U12" t="n">
-        <v>0.06161609124085275</v>
+        <v>0.8316369136646375</v>
       </c>
       <c r="V12" t="n">
-        <v>0.07226913686127913</v>
+        <v>1.080205370496956</v>
       </c>
       <c r="W12" t="n">
-        <v>0.08292218248170551</v>
+        <v>1.328773827329275</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
@@ -2174,22 +2174,22 @@
         <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0178906878969427</v>
+        <v>0.06397952655149648</v>
       </c>
       <c r="AA12" t="n">
-        <v>85629.6573827</v>
+        <v>4859.12838</v>
       </c>
       <c r="AB12" t="n">
-        <v>22461.6916809</v>
+        <v>6306.343639</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.187796</v>
+        <v>39.151452</v>
       </c>
       <c r="AD12" t="n">
-        <v>36.924287</v>
+        <v>127.289717</v>
       </c>
       <c r="AE12" t="n">
-        <v>290786787.6452953</v>
+        <v>143080254.7114663</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BERAUSDT</t>
+          <t>MOODENGUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Berachain</t>
+          <t>Moo Deng (moodengsol.com)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2233,15 +2233,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>83.68000000000001</v>
+        <v>66.08799999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>83.68000000000001</v>
+        <v>82.61</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>none</t>
@@ -2256,13 +2260,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5830684568323188</v>
+        <v>0.05069032494417323</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.05351</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.009498379156611</v>
+        <v>5.562550760785534</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2270,43 +2274,43 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.3345</v>
+        <v>0.038</v>
       </c>
       <c r="T13" t="n">
-        <v>42.63109312802409</v>
+        <v>25.03500413175388</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8316369136646375</v>
+        <v>0.06338064988834646</v>
       </c>
       <c r="V13" t="n">
-        <v>1.080205370496956</v>
+        <v>0.07607097483251971</v>
       </c>
       <c r="W13" t="n">
-        <v>1.328773827329275</v>
+        <v>0.08876129977669295</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0.9999999999999994</v>
       </c>
       <c r="Y13" t="n">
         <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0471883602044777</v>
+        <v>0.09344921035417519</v>
       </c>
       <c r="AA13" t="n">
-        <v>5905.691436</v>
+        <v>11526.3521805</v>
       </c>
       <c r="AB13" t="n">
-        <v>5813.458148</v>
+        <v>7202.9094664</v>
       </c>
       <c r="AC13" t="n">
-        <v>47.930978</v>
+        <v>27.742796</v>
       </c>
       <c r="AD13" t="n">
-        <v>140.334752</v>
+        <v>3294.336159</v>
       </c>
       <c r="AE13" t="n">
-        <v>145893974.843575</v>
+        <v>53112472.07965237</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -2321,12 +2325,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MEWUSDT</t>
+          <t>BBUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cat in a dogs world</t>
+          <t>BounceBit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2336,7 +2340,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_too_early</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2350,10 +2354,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>83.11</v>
+        <v>65.93600000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>83.11</v>
+        <v>82.42</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2377,57 +2381,57 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0006117059688524329</v>
+        <v>0.02786894629479462</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0006677</v>
+        <v>0.02767</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.153749349971619</v>
+        <v>-0.7138637130022385</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>early</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0.0004931</v>
+        <v>0.0235</v>
       </c>
       <c r="T14" t="n">
-        <v>19.38937576086416</v>
+        <v>15.67675450869363</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0007303119377048658</v>
+        <v>0.03223789258958924</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0008489179065572987</v>
+        <v>0.03660683888438386</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0009675238754097315</v>
+        <v>0.04097578517917849</v>
       </c>
       <c r="X14" t="n">
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.1491646778042996</v>
+        <v>0.1084402674859887</v>
       </c>
       <c r="AA14" t="n">
-        <v>2254.179395386</v>
+        <v>6602.2553133</v>
       </c>
       <c r="AB14" t="n">
-        <v>3426.01319183</v>
+        <v>1255.2760289</v>
       </c>
       <c r="AC14" t="n">
-        <v>2981.251551</v>
+        <v>127.73085</v>
       </c>
       <c r="AD14" t="n">
-        <v>20930.119973</v>
+        <v>221.811781</v>
       </c>
       <c r="AE14" t="n">
-        <v>59356148.43775055</v>
+        <v>28889644.70188995</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
@@ -2442,12 +2446,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MOODENGUSDT</t>
+          <t>HUMAUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Moo Deng (moodengsol.com)</t>
+          <t>Huma Finance</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2457,7 +2461,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2471,19 +2475,15 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>82.61</v>
+        <v>63.52</v>
       </c>
       <c r="I15" t="n">
-        <v>82.61</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>none</t>
@@ -2498,13 +2498,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.05069032494417323</v>
+        <v>0.01575536570152586</v>
       </c>
       <c r="P15" t="n">
-        <v>0.05501</v>
+        <v>0.01753</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.521695334532087</v>
+        <v>11.26368205025079</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2512,43 +2512,43 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>0.038</v>
+        <v>0.01102</v>
       </c>
       <c r="T15" t="n">
-        <v>25.03500413175388</v>
+        <v>30.05557466093761</v>
       </c>
       <c r="U15" t="n">
-        <v>0.06338064988834646</v>
+        <v>0.02049073140305172</v>
       </c>
       <c r="V15" t="n">
-        <v>0.07607097483251971</v>
+        <v>0.02522609710457759</v>
       </c>
       <c r="W15" t="n">
-        <v>0.08876129977669295</v>
+        <v>0.02996146280610345</v>
       </c>
       <c r="X15" t="n">
-        <v>0.9999999999999994</v>
+        <v>0.9999999999999997</v>
       </c>
       <c r="Y15" t="n">
         <v>2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.1089720305121641</v>
+        <v>0.0570613409415098</v>
       </c>
       <c r="AA15" t="n">
-        <v>7919.2778208</v>
+        <v>5229.3499519</v>
       </c>
       <c r="AB15" t="n">
-        <v>5567.2391854</v>
+        <v>12676.771829</v>
       </c>
       <c r="AC15" t="n">
-        <v>39.657217</v>
+        <v>13.238501</v>
       </c>
       <c r="AD15" t="n">
-        <v>3088.525251</v>
+        <v>96.207116</v>
       </c>
       <c r="AE15" t="n">
-        <v>54631214.16419438</v>
+        <v>51062035.87446485</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BBUSDT</t>
+          <t>RESOLVUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BounceBit</t>
+          <t>Resolv</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2578,31 +2578,31 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | rebound_not_confirmed | entry_too_early</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>82.42</v>
+        <v>61.2</v>
       </c>
       <c r="I16" t="n">
-        <v>82.42</v>
+        <v>68</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>retest_not_reclaimed</t>
+          <t>rebound_not_confirmed</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2619,57 +2619,57 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02786894629479462</v>
+        <v>0.09645174982689825</v>
       </c>
       <c r="P16" t="n">
-        <v>0.02824</v>
+        <v>0.07854999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.331423518063501</v>
+        <v>-18.56031628148425</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>early</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0.0235</v>
+        <v>0.09490090622717488</v>
       </c>
       <c r="T16" t="n">
-        <v>15.67675450869363</v>
+        <v>1.607895763951053</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03223789258958924</v>
+        <v>0.09800259342662161</v>
       </c>
       <c r="V16" t="n">
-        <v>0.03660683888438386</v>
+        <v>0.09955343702634498</v>
       </c>
       <c r="W16" t="n">
-        <v>0.04097578517917849</v>
+        <v>0.1011042806260683</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.999999999999999</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.2123142250530699</v>
+        <v>0.1274534794799934</v>
       </c>
       <c r="AA16" t="n">
-        <v>70.82748410000001</v>
+        <v>18792.5830865</v>
       </c>
       <c r="AB16" t="n">
-        <v>2488.898018</v>
+        <v>16851.7567472</v>
       </c>
       <c r="AC16" t="n">
-        <v>109.980239</v>
+        <v>35.63184</v>
       </c>
       <c r="AD16" t="n">
-        <v>232.629813</v>
+        <v>65.257327</v>
       </c>
       <c r="AE16" t="n">
-        <v>29586251.68316404</v>
+        <v>29111845.02402832</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HUMAUSDT</t>
+          <t>RSRUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Huma Finance</t>
+          <t>Reserve Rights</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2713,15 +2713,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>79.40000000000001</v>
+        <v>60.008</v>
       </c>
       <c r="I17" t="n">
-        <v>79.40000000000001</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>none</t>
@@ -2736,13 +2740,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01575536570152586</v>
+        <v>0.00160169917178106</v>
       </c>
       <c r="P17" t="n">
-        <v>0.01779</v>
+        <v>0.001756</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.91391350108166</v>
+        <v>9.633571081101366</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2750,43 +2754,43 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>0.01102</v>
+        <v>0.001341</v>
       </c>
       <c r="T17" t="n">
-        <v>30.05557466093761</v>
+        <v>16.27641297280357</v>
       </c>
       <c r="U17" t="n">
-        <v>0.02049073140305172</v>
+        <v>0.001862398343562119</v>
       </c>
       <c r="V17" t="n">
-        <v>0.02522609710457759</v>
+        <v>0.002123097515343179</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02996146280610345</v>
+        <v>0.002383796687124239</v>
       </c>
       <c r="X17" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1123595505617932</v>
+        <v>0.05683432793407973</v>
       </c>
       <c r="AA17" t="n">
-        <v>9710.5522798</v>
+        <v>9891.07759083</v>
       </c>
       <c r="AB17" t="n">
-        <v>7919.2200761</v>
+        <v>12581.41283404</v>
       </c>
       <c r="AC17" t="n">
-        <v>26.119856</v>
+        <v>34.171257</v>
       </c>
       <c r="AD17" t="n">
-        <v>139.34221</v>
+        <v>109.38859</v>
       </c>
       <c r="AE17" t="n">
-        <v>51415963.27353501</v>
+        <v>109789465.2251928</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -2801,12 +2805,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RSRUSDT</t>
+          <t>ETHFIUSDT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Reserve Rights</t>
+          <t>ether.fi</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2816,7 +2820,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2830,40 +2834,36 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>75.01000000000001</v>
+        <v>58.736</v>
       </c>
       <c r="I18" t="n">
-        <v>75.01000000000001</v>
+        <v>73.42</v>
       </c>
       <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N18" t="b">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.00160169917178106</v>
+        <v>0.5306211633169757</v>
       </c>
       <c r="P18" t="n">
-        <v>0.001785</v>
+        <v>0.5471</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.44414828004894</v>
+        <v>3.105574715492532</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2871,19 +2871,19 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>0.001341</v>
+        <v>0.3792</v>
       </c>
       <c r="T18" t="n">
-        <v>16.27641297280357</v>
+        <v>28.53658575742138</v>
       </c>
       <c r="U18" t="n">
-        <v>0.001862398343562119</v>
+        <v>0.6820423266339515</v>
       </c>
       <c r="V18" t="n">
-        <v>0.002123097515343179</v>
+        <v>0.8334634899509272</v>
       </c>
       <c r="W18" t="n">
-        <v>0.002383796687124239</v>
+        <v>0.984884653267903</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
@@ -2892,22 +2892,22 @@
         <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.05600672080650421</v>
+        <v>0.05481955230698345</v>
       </c>
       <c r="AA18" t="n">
-        <v>10935.05094315</v>
+        <v>152420.669825</v>
       </c>
       <c r="AB18" t="n">
-        <v>8860.99198787</v>
+        <v>192009.143558</v>
       </c>
       <c r="AC18" t="n">
-        <v>35.662142</v>
+        <v>13.444725</v>
       </c>
       <c r="AD18" t="n">
-        <v>125.648143</v>
+        <v>21.968995</v>
       </c>
       <c r="AE18" t="n">
-        <v>111808609.7241988</v>
+        <v>407073036.653609</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
@@ -2922,12 +2922,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ETHFIUSDT</t>
+          <t>JSTUSDT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ether.fi</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2937,24 +2937,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>73.42</v>
+        <v>58.32</v>
       </c>
       <c r="I19" t="n">
-        <v>73.42</v>
+        <v>64.8</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -2962,25 +2962,25 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N19" t="b">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5306211633169757</v>
+        <v>0.05283073888656207</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5497</v>
+        <v>0.05559</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.595566479813983</v>
+        <v>5.222832713664305</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2988,19 +2988,19 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0.3792</v>
+        <v>0.05121085551843595</v>
       </c>
       <c r="T19" t="n">
-        <v>28.53658575742138</v>
+        <v>3.066175870839743</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6820423266339515</v>
+        <v>0.05445062225468818</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8334634899509272</v>
+        <v>0.0560705056228143</v>
       </c>
       <c r="W19" t="n">
-        <v>0.984884653267903</v>
+        <v>0.05769038899094042</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
@@ -3009,22 +3009,22 @@
         <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.05458018739197071</v>
+        <v>0.05401026194976201</v>
       </c>
       <c r="AA19" t="n">
-        <v>169877.897567</v>
+        <v>4254.1169366</v>
       </c>
       <c r="AB19" t="n">
-        <v>177357.671819</v>
+        <v>2820.683811</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.326483</v>
+        <v>67.95941000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>22.102485</v>
+        <v>2998.790419</v>
       </c>
       <c r="AE19" t="n">
-        <v>408850445.490566</v>
+        <v>490006042.6826856</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -3039,12 +3039,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CYBERUSDT</t>
+          <t>NAORISUSDT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Naoris Protocol</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3054,33 +3054,29 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>71.83</v>
+        <v>58.32</v>
       </c>
       <c r="I20" t="n">
-        <v>71.83</v>
+        <v>64.8</v>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>none</t>
@@ -3095,13 +3091,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5488674060370984</v>
+        <v>0.06137695176902147</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5707</v>
+        <v>0.07275</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.977753774911874</v>
+        <v>18.52983555419707</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3109,43 +3105,43 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>0.4252</v>
+        <v>0.05160960220824248</v>
       </c>
       <c r="T20" t="n">
-        <v>22.5313809267697</v>
+        <v>15.91370910294836</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6725348120741967</v>
+        <v>0.07114430132980046</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7962022181112951</v>
+        <v>0.08091165089057946</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9198696241483935</v>
+        <v>0.09067900045135846</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0.9999999999999993</v>
       </c>
       <c r="Y20" t="n">
         <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.1401541695865492</v>
+        <v>0.2759001241550638</v>
       </c>
       <c r="AA20" t="n">
-        <v>12412.899518</v>
+        <v>7380.564213199999</v>
       </c>
       <c r="AB20" t="n">
-        <v>5634.295698999999</v>
+        <v>6734.0402046</v>
       </c>
       <c r="AC20" t="n">
-        <v>67.433243</v>
+        <v>39.388101</v>
       </c>
       <c r="AD20" t="n">
-        <v>382.55067</v>
+        <v>566.595345</v>
       </c>
       <c r="AE20" t="n">
-        <v>36653386.36226889</v>
+        <v>43297744.72711914</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -3160,12 +3156,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RESOLVUSDT</t>
+          <t>CYBERUSDT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Resolv</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3175,31 +3171,31 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | rebound_not_confirmed | entry_too_early</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>68</v>
+        <v>57.464</v>
       </c>
       <c r="I21" t="n">
-        <v>68</v>
+        <v>71.83</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>rebound_not_confirmed</t>
+          <t>retest_not_reclaimed</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3216,33 +3212,33 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.09645174982689825</v>
+        <v>0.5488674060370984</v>
       </c>
       <c r="P21" t="n">
-        <v>0.07897999999999999</v>
+        <v>0.5645</v>
       </c>
       <c r="Q21" t="n">
-        <v>-18.11449751637971</v>
+        <v>2.848154907898648</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>early</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>0.09490090622717488</v>
+        <v>0.4252</v>
       </c>
       <c r="T21" t="n">
-        <v>1.607895763951053</v>
+        <v>22.5313809267697</v>
       </c>
       <c r="U21" t="n">
-        <v>0.09800259342662161</v>
+        <v>0.6725348120741967</v>
       </c>
       <c r="V21" t="n">
-        <v>0.09955343702634498</v>
+        <v>0.7962022181112951</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1011042806260683</v>
+        <v>0.9198696241483935</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -3251,22 +3247,22 @@
         <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.1646507504274652</v>
+        <v>0.1240365021706448</v>
       </c>
       <c r="AA21" t="n">
-        <v>15184.8941931</v>
+        <v>16996.499024</v>
       </c>
       <c r="AB21" t="n">
-        <v>17940.57161</v>
+        <v>1094.503648</v>
       </c>
       <c r="AC21" t="n">
-        <v>26.052516</v>
+        <v>92.717097</v>
       </c>
       <c r="AD21" t="n">
-        <v>57.485572</v>
+        <v>291.077853</v>
       </c>
       <c r="AE21" t="n">
-        <v>29299357.59923158</v>
+        <v>36363206.15177908</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -3287,7 +3283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3492,125 +3488,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TRUMPUSDT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OFFICIAL TRUMP</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ENTER</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>entry_chased</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>reversal</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>reversal_base_reclaim</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>70</v>
-      </c>
-      <c r="I2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>DIRECT_OK</t>
-        </is>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3.273047884957256</v>
-      </c>
-      <c r="P2" t="n">
-        <v>4.118</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>25.81545228611217</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>chased</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>3.035</v>
-      </c>
-      <c r="T2" t="n">
-        <v>7.27297287801107</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.511095769914513</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3.749143654871769</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.987191539829025</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.02429248147699099</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>206131.8757</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>170725.24125</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.187364</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>9.366531999999999</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>963082486.9768051</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>RISK_OFF</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AG2"/>
+  <autoFilter ref="A1:AG1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3828,7 +3707,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -3847,7 +3726,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3861,7 +3740,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>79.95999999999999</v>
+        <v>63.968</v>
       </c>
       <c r="I2" t="n">
         <v>79.95999999999999</v>
@@ -3891,14 +3770,14 @@
         <v>0.02640959622869432</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02667</v>
+        <v>0.02638</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9860195099186786</v>
+        <v>-0.1120661915389953</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>at_trigger</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -3923,22 +3802,22 @@
         <v>1.999999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.07499062617172549</v>
+        <v>0.03791469194312642</v>
       </c>
       <c r="AA2" t="n">
-        <v>23659.2173889</v>
+        <v>22533.0120156</v>
       </c>
       <c r="AB2" t="n">
-        <v>9723.495884900001</v>
+        <v>12251.9781237</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.878727</v>
+        <v>12.498956</v>
       </c>
       <c r="AD2" t="n">
-        <v>368.625046</v>
+        <v>254.069237</v>
       </c>
       <c r="AE2" t="n">
-        <v>234117444.5360853</v>
+        <v>237286526.8349056</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -3949,7 +3828,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -3982,7 +3861,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>77.98999999999999</v>
+        <v>62.392</v>
       </c>
       <c r="I3" t="n">
         <v>77.98999999999999</v>
@@ -4012,10 +3891,10 @@
         <v>0.001010902989841661</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0011675</v>
+        <v>0.001141</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.4908049270748</v>
+        <v>12.86938622851592</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -4044,22 +3923,22 @@
         <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1109830537414168</v>
+        <v>0.192796424502668</v>
       </c>
       <c r="AA3" t="n">
-        <v>13996.687216901</v>
+        <v>9881.433054928</v>
       </c>
       <c r="AB3" t="n">
-        <v>9804.828149494</v>
+        <v>8495.584516289</v>
       </c>
       <c r="AC3" t="n">
-        <v>40.428812</v>
+        <v>37.834685</v>
       </c>
       <c r="AD3" t="n">
-        <v>341.071642</v>
+        <v>369.950816</v>
       </c>
       <c r="AE3" t="n">
-        <v>80281438.96733324</v>
+        <v>79003732.82059467</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -4070,7 +3949,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -4089,7 +3968,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4103,7 +3982,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>77.73</v>
+        <v>62.184</v>
       </c>
       <c r="I4" t="n">
         <v>77.73</v>
@@ -4118,12 +3997,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N4" t="b">
@@ -4133,10 +4012,10 @@
         <v>0.0881281822103617</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09425</v>
+        <v>0.09217</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.946492751916233</v>
+        <v>4.58629429118429</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -4165,22 +4044,22 @@
         <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2016449986733836</v>
+        <v>0.1086130118388063</v>
       </c>
       <c r="AA4" t="n">
-        <v>69045.23505849999</v>
+        <v>58469.0676636</v>
       </c>
       <c r="AB4" t="n">
-        <v>72640.4795687</v>
+        <v>54732.5031165</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.985773</v>
+        <v>26.451381</v>
       </c>
       <c r="AD4" t="n">
-        <v>21.205293</v>
+        <v>30.931245</v>
       </c>
       <c r="AE4" t="n">
-        <v>838849995.5801125</v>
+        <v>821498659.5548553</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -4191,16 +4070,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MELANIAUSDT</t>
+          <t>BANANAS31USDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Official Melania Meme</t>
+          <t>Banana For Scale</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4210,24 +4089,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_chased</t>
+          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>75.43000000000001</v>
+        <v>61.2</v>
       </c>
       <c r="I5" t="n">
-        <v>75.43000000000001</v>
+        <v>68</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -4247,13 +4126,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1112803252979652</v>
+        <v>0.008539124282940763</v>
       </c>
       <c r="P5" t="n">
-        <v>0.12622</v>
+        <v>0.01074</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.42526152941432</v>
+        <v>25.774021364885</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -4261,19 +4140,19 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.10264</v>
+        <v>0.007486231252880395</v>
       </c>
       <c r="T5" t="n">
-        <v>7.764468044849582</v>
+        <v>12.33022257520962</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1199206505959303</v>
+        <v>0.009592017313001132</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1285609758938955</v>
+        <v>0.0106449103430615</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1372013011918607</v>
+        <v>0.01169780337312187</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -4282,46 +4161,42 @@
         <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2771289441387143</v>
+        <v>0.03074443455860293</v>
       </c>
       <c r="AA5" t="n">
-        <v>2941.1854253</v>
+        <v>9597.195318724</v>
       </c>
       <c r="AB5" t="n">
-        <v>3019.6961802</v>
+        <v>17536.443041871</v>
       </c>
       <c r="AC5" t="n">
-        <v>82.148719</v>
+        <v>21.126211</v>
       </c>
       <c r="AD5" t="n">
-        <v>3097.201671</v>
+        <v>82.92800800000001</v>
       </c>
       <c r="AE5" t="n">
-        <v>126640131.3049714</v>
+        <v>107477184.4761735</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>low_liquidity</t>
-        </is>
-      </c>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BANANAS31USDT</t>
+          <t>RIVERUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Banana For Scale</t>
+          <t>River</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4345,7 +4220,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>68</v>
+        <v>61.2</v>
       </c>
       <c r="I6" t="n">
         <v>68</v>
@@ -4368,13 +4243,13 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008539124282940763</v>
+        <v>18.16763992150123</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0109933</v>
+        <v>21.814</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.7403676974479</v>
+        <v>20.07063159691609</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -4382,19 +4257,19 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.007486231252880395</v>
+        <v>16.49196841873954</v>
       </c>
       <c r="T6" t="n">
-        <v>12.33022257520962</v>
+        <v>9.223385701180424</v>
       </c>
       <c r="U6" t="n">
-        <v>0.009592017313001132</v>
+        <v>19.84331142426293</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0106449103430615</v>
+        <v>21.51898292702462</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01169780337312187</v>
+        <v>23.19465442978631</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -4403,22 +4278,22 @@
         <v>2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02823816615884125</v>
+        <v>0.1452886923098024</v>
       </c>
       <c r="AA6" t="n">
-        <v>8759.795877918001</v>
+        <v>12996.092697</v>
       </c>
       <c r="AB6" t="n">
-        <v>10741.506298575</v>
+        <v>9155.83409</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.40979</v>
+        <v>47.281283</v>
       </c>
       <c r="AD6" t="n">
-        <v>74.307877</v>
+        <v>107.994066</v>
       </c>
       <c r="AE6" t="n">
-        <v>109297486.2205953</v>
+        <v>425424556.8357913</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -4429,16 +4304,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RIVERUSDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4448,7 +4323,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+          <t>btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4462,7 +4337,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>68</v>
+        <v>61.2</v>
       </c>
       <c r="I7" t="n">
         <v>68</v>
@@ -4473,25 +4348,25 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>18.16763992150123</v>
+        <v>219.1247632833021</v>
       </c>
       <c r="P7" t="n">
-        <v>21.58</v>
+        <v>237.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.78262720553079</v>
+        <v>8.39943256112139</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -4499,19 +4374,19 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>16.49196841873954</v>
+        <v>204.2569217840868</v>
       </c>
       <c r="T7" t="n">
-        <v>9.223385701180424</v>
+        <v>6.78510327926425</v>
       </c>
       <c r="U7" t="n">
-        <v>19.84331142426293</v>
+        <v>233.9926047825175</v>
       </c>
       <c r="V7" t="n">
-        <v>21.51898292702462</v>
+        <v>248.8604462817329</v>
       </c>
       <c r="W7" t="n">
-        <v>23.19465442978631</v>
+        <v>263.7282877809482</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
@@ -4520,22 +4395,22 @@
         <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0356526872634239</v>
+        <v>0.05898462186643622</v>
       </c>
       <c r="AA7" t="n">
-        <v>15653.537735</v>
+        <v>226657.46683</v>
       </c>
       <c r="AB7" t="n">
-        <v>16345.548524</v>
+        <v>203045.18005</v>
       </c>
       <c r="AC7" t="n">
-        <v>26.460085</v>
+        <v>4.694521</v>
       </c>
       <c r="AD7" t="n">
-        <v>82.540488</v>
+        <v>8.198316</v>
       </c>
       <c r="AE7" t="n">
-        <v>423313573.005538</v>
+        <v>2551194347.267691</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -4546,16 +4421,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TAOUSDT</t>
+          <t>MELANIAUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Official Melania Meme</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4565,24 +4440,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>68</v>
+        <v>60.344</v>
       </c>
       <c r="I8" t="n">
-        <v>68</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -4590,25 +4465,25 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>219.1247632833021</v>
+        <v>0.1112803252979652</v>
       </c>
       <c r="P8" t="n">
-        <v>245.26</v>
+        <v>0.12347</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.92710322881587</v>
+        <v>10.95402504386616</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -4616,19 +4491,19 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>204.2569217840868</v>
+        <v>0.10264</v>
       </c>
       <c r="T8" t="n">
-        <v>6.78510327926425</v>
+        <v>7.764468044849582</v>
       </c>
       <c r="U8" t="n">
-        <v>233.9926047825175</v>
+        <v>0.1199206505959303</v>
       </c>
       <c r="V8" t="n">
-        <v>248.8604462817329</v>
+        <v>0.1285609758938955</v>
       </c>
       <c r="W8" t="n">
-        <v>263.7282877809482</v>
+        <v>0.1372013011918607</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -4637,29 +4512,33 @@
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.05298445110146337</v>
+        <v>0.3883180972413302</v>
       </c>
       <c r="AA8" t="n">
-        <v>228919.5366</v>
+        <v>2868.5310179</v>
       </c>
       <c r="AB8" t="n">
-        <v>188786.67372</v>
+        <v>4581.8561025</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.717844</v>
+        <v>65.49919800000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>9.054069999999999</v>
+        <v>2669.233357</v>
       </c>
       <c r="AE8" t="n">
-        <v>2626472896.404871</v>
+        <v>123955104.8551496</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>low_liquidity</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AG8"/>
